--- a/tests/worked_examples/staged/two_stages_envelope_then_heat_pump.xlsx
+++ b/tests/worked_examples/staged/two_stages_envelope_then_heat_pump.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>the staged-evaluator harness (tests/worked_example_runners.py::_staged_values), 2026-09-19</t>
+          <t>the staged-evaluator harness (tests/worked_example_runners.py::_staged_values), 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -517,6 +517,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -822,6 +823,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -836,7 +838,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>73699.46884345633</v>
+        <v>64019.36515098041</v>
       </c>
       <c r="C39" t="n">
         <v>0.01</v>
@@ -854,7 +856,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4953.761947825587</v>
+        <v>4303.10692852485</v>
       </c>
       <c r="C40" t="n">
         <v>0.01</v>
@@ -890,7 +892,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28198.72811320526</v>
+        <v>18518.62442072934</v>
       </c>
       <c r="C42" t="n">
         <v>0.01</v>
@@ -908,7 +910,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1895.397463460535</v>
+        <v>1244.742444159798</v>
       </c>
       <c r="C43" t="n">
         <v>0.01</v>
@@ -1070,7 +1072,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-12652.56509264953</v>
+        <v>-7231.674189984586</v>
       </c>
       <c r="C52" t="n">
         <v>0.01</v>

--- a/tests/worked_examples/staged/two_stages_envelope_then_heat_pump.xlsx
+++ b/tests/worked_examples/staged/two_stages_envelope_then_heat_pump.xlsx
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64019.36515098041</v>
+        <v>68011.95102056063</v>
       </c>
       <c r="C39" t="n">
         <v>0.01</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4303.10692852485</v>
+        <v>4571.471412889906</v>
       </c>
       <c r="C40" t="n">
         <v>0.01</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18518.62442072934</v>
+        <v>22511.21029030957</v>
       </c>
       <c r="C42" t="n">
         <v>0.01</v>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1244.742444159798</v>
+        <v>1513.106928524853</v>
       </c>
       <c r="C43" t="n">
         <v>0.01</v>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-7231.674189984586</v>
+        <v>-8788.6007294068</v>
       </c>
       <c r="C52" t="n">
         <v>0.01</v>
